--- a/Result/profitability/2617.xlsx
+++ b/Result/profitability/2617.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.43</v>
       </c>
       <c r="M2" t="n">
-        <v>0.87625</v>
+        <v>0.86</v>
       </c>
       <c r="N2" t="n">
-        <v>43.78375</v>
+        <v>44.06375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.82</v>
       </c>
       <c r="M3" t="n">
-        <v>0.98375</v>
+        <v>0.9962500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>45.38625</v>
+        <v>45.59875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>2.73</v>
       </c>
       <c r="M4" t="n">
-        <v>1.23375</v>
+        <v>1.265</v>
       </c>
       <c r="N4" t="n">
-        <v>47.98</v>
+        <v>48.81125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>2.04</v>
       </c>
       <c r="M5" t="n">
-        <v>1.41625</v>
+        <v>1.46625</v>
       </c>
       <c r="N5" t="n">
-        <v>50.50125</v>
+        <v>51.15125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>2.06</v>
       </c>
       <c r="M6" t="n">
-        <v>1.62</v>
+        <v>1.555</v>
       </c>
       <c r="N6" t="n">
-        <v>53.29</v>
+        <v>53.61125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>1.5525</v>
+        <v>1.55375</v>
       </c>
       <c r="N7" t="n">
-        <v>54.15125</v>
+        <v>53.975</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>1.52</v>
+        <v>1.535</v>
       </c>
       <c r="N8" t="n">
-        <v>52.89</v>
+        <v>53.24375000000001</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>1.3675</v>
       </c>
       <c r="N11" t="n">
-        <v>48.32624999999999</v>
+        <v>48.32625</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2617</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1287</v>
+      </c>
+      <c r="D75" t="n">
+        <v>710</v>
+      </c>
+      <c r="E75" t="n">
+        <v>577</v>
+      </c>
+      <c r="F75" t="n">
+        <v>44.82</v>
+      </c>
+      <c r="G75" t="n">
+        <v>529</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>41.13%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-55</v>
+      </c>
+      <c r="J75" t="n">
+        <v>474</v>
+      </c>
+      <c r="K75" t="n">
+        <v>348</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.80125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>42.3475</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1690140845070423</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.829999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.0673969992855441</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.9302325581395348</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.200000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1312468450277637</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
